--- a/Plano de Projeto/Cronograma.xlsx
+++ b/Plano de Projeto/Cronograma.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guiba\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guiba\Desktop\LDS\Plano de Projeto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD505C32-2CC6-4B61-9C04-835172ED05F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8736636C-F279-4294-96B1-94208074A2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1048,6 +1048,24 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1058,27 +1076,9 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="31" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1683,26 +1683,26 @@
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="44" t="s">
+      <c r="K1" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
-      <c r="AB1" s="44"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
       <c r="AC1" s="42"/>
       <c r="AD1" s="42"/>
       <c r="AE1" s="42"/>
@@ -1742,191 +1742,191 @@
       <c r="B4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="49">
+      <c r="C4" s="52">
         <v>45915</v>
       </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="43" t="s">
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="43"/>
+      <c r="G4" s="49"/>
       <c r="H4" s="30">
         <v>1</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="6"/>
-      <c r="K4" s="46" t="str">
+      <c r="K4" s="43" t="str">
         <f>"Semana "&amp;(K6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Semana 1</v>
       </c>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="46" t="str">
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="45"/>
+      <c r="R4" s="43" t="str">
         <f>"Semana "&amp;(R6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Semana 2</v>
       </c>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="W4" s="47"/>
-      <c r="X4" s="48"/>
-      <c r="Y4" s="46" t="str">
+      <c r="S4" s="44"/>
+      <c r="T4" s="44"/>
+      <c r="U4" s="44"/>
+      <c r="V4" s="44"/>
+      <c r="W4" s="44"/>
+      <c r="X4" s="45"/>
+      <c r="Y4" s="43" t="str">
         <f>"Semana "&amp;(Y6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Semana 3</v>
       </c>
-      <c r="Z4" s="47"/>
-      <c r="AA4" s="47"/>
-      <c r="AB4" s="47"/>
-      <c r="AC4" s="47"/>
-      <c r="AD4" s="47"/>
-      <c r="AE4" s="48"/>
-      <c r="AF4" s="46" t="str">
+      <c r="Z4" s="44"/>
+      <c r="AA4" s="44"/>
+      <c r="AB4" s="44"/>
+      <c r="AC4" s="44"/>
+      <c r="AD4" s="44"/>
+      <c r="AE4" s="45"/>
+      <c r="AF4" s="43" t="str">
         <f>"Semana "&amp;(AF6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Semana 4</v>
       </c>
-      <c r="AG4" s="47"/>
-      <c r="AH4" s="47"/>
-      <c r="AI4" s="47"/>
-      <c r="AJ4" s="47"/>
-      <c r="AK4" s="47"/>
-      <c r="AL4" s="48"/>
-      <c r="AM4" s="46" t="str">
+      <c r="AG4" s="44"/>
+      <c r="AH4" s="44"/>
+      <c r="AI4" s="44"/>
+      <c r="AJ4" s="44"/>
+      <c r="AK4" s="44"/>
+      <c r="AL4" s="45"/>
+      <c r="AM4" s="43" t="str">
         <f>"Semana "&amp;(AM6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Semana 5</v>
       </c>
-      <c r="AN4" s="47"/>
-      <c r="AO4" s="47"/>
-      <c r="AP4" s="47"/>
-      <c r="AQ4" s="47"/>
-      <c r="AR4" s="47"/>
-      <c r="AS4" s="48"/>
-      <c r="AT4" s="46" t="str">
+      <c r="AN4" s="44"/>
+      <c r="AO4" s="44"/>
+      <c r="AP4" s="44"/>
+      <c r="AQ4" s="44"/>
+      <c r="AR4" s="44"/>
+      <c r="AS4" s="45"/>
+      <c r="AT4" s="43" t="str">
         <f>"Semana "&amp;(AT6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Semana 6</v>
       </c>
-      <c r="AU4" s="47"/>
-      <c r="AV4" s="47"/>
-      <c r="AW4" s="47"/>
-      <c r="AX4" s="47"/>
-      <c r="AY4" s="47"/>
-      <c r="AZ4" s="48"/>
-      <c r="BA4" s="46" t="str">
+      <c r="AU4" s="44"/>
+      <c r="AV4" s="44"/>
+      <c r="AW4" s="44"/>
+      <c r="AX4" s="44"/>
+      <c r="AY4" s="44"/>
+      <c r="AZ4" s="45"/>
+      <c r="BA4" s="43" t="str">
         <f>"Semana "&amp;(BA6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Semana 7</v>
       </c>
-      <c r="BB4" s="47"/>
-      <c r="BC4" s="47"/>
-      <c r="BD4" s="47"/>
-      <c r="BE4" s="47"/>
-      <c r="BF4" s="47"/>
-      <c r="BG4" s="48"/>
-      <c r="BH4" s="46" t="str">
+      <c r="BB4" s="44"/>
+      <c r="BC4" s="44"/>
+      <c r="BD4" s="44"/>
+      <c r="BE4" s="44"/>
+      <c r="BF4" s="44"/>
+      <c r="BG4" s="45"/>
+      <c r="BH4" s="43" t="str">
         <f>"Semana "&amp;(BH6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Semana 8</v>
       </c>
-      <c r="BI4" s="47"/>
-      <c r="BJ4" s="47"/>
-      <c r="BK4" s="47"/>
-      <c r="BL4" s="47"/>
-      <c r="BM4" s="47"/>
-      <c r="BN4" s="48"/>
+      <c r="BI4" s="44"/>
+      <c r="BJ4" s="44"/>
+      <c r="BK4" s="44"/>
+      <c r="BL4" s="44"/>
+      <c r="BM4" s="44"/>
+      <c r="BN4" s="45"/>
     </row>
     <row r="5" spans="1:66" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="19"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
       <c r="F5" s="18"/>
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="18"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="50">
+      <c r="K5" s="46">
         <f>K6</f>
         <v>45915</v>
       </c>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="51"/>
-      <c r="O5" s="51"/>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="50">
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="46">
         <f>R6</f>
         <v>45922</v>
       </c>
-      <c r="S5" s="51"/>
-      <c r="T5" s="51"/>
-      <c r="U5" s="51"/>
-      <c r="V5" s="51"/>
-      <c r="W5" s="51"/>
-      <c r="X5" s="52"/>
-      <c r="Y5" s="50">
+      <c r="S5" s="47"/>
+      <c r="T5" s="47"/>
+      <c r="U5" s="47"/>
+      <c r="V5" s="47"/>
+      <c r="W5" s="47"/>
+      <c r="X5" s="48"/>
+      <c r="Y5" s="46">
         <f>Y6</f>
         <v>45929</v>
       </c>
-      <c r="Z5" s="51"/>
-      <c r="AA5" s="51"/>
-      <c r="AB5" s="51"/>
-      <c r="AC5" s="51"/>
-      <c r="AD5" s="51"/>
-      <c r="AE5" s="52"/>
-      <c r="AF5" s="50">
+      <c r="Z5" s="47"/>
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="47"/>
+      <c r="AD5" s="47"/>
+      <c r="AE5" s="48"/>
+      <c r="AF5" s="46">
         <f>AF6</f>
         <v>45936</v>
       </c>
-      <c r="AG5" s="51"/>
-      <c r="AH5" s="51"/>
-      <c r="AI5" s="51"/>
-      <c r="AJ5" s="51"/>
-      <c r="AK5" s="51"/>
-      <c r="AL5" s="52"/>
-      <c r="AM5" s="50">
+      <c r="AG5" s="47"/>
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="47"/>
+      <c r="AJ5" s="47"/>
+      <c r="AK5" s="47"/>
+      <c r="AL5" s="48"/>
+      <c r="AM5" s="46">
         <f>AM6</f>
         <v>45943</v>
       </c>
-      <c r="AN5" s="51"/>
-      <c r="AO5" s="51"/>
-      <c r="AP5" s="51"/>
-      <c r="AQ5" s="51"/>
-      <c r="AR5" s="51"/>
-      <c r="AS5" s="52"/>
-      <c r="AT5" s="50">
+      <c r="AN5" s="47"/>
+      <c r="AO5" s="47"/>
+      <c r="AP5" s="47"/>
+      <c r="AQ5" s="47"/>
+      <c r="AR5" s="47"/>
+      <c r="AS5" s="48"/>
+      <c r="AT5" s="46">
         <f>AT6</f>
         <v>45950</v>
       </c>
-      <c r="AU5" s="51"/>
-      <c r="AV5" s="51"/>
-      <c r="AW5" s="51"/>
-      <c r="AX5" s="51"/>
-      <c r="AY5" s="51"/>
-      <c r="AZ5" s="52"/>
-      <c r="BA5" s="50">
+      <c r="AU5" s="47"/>
+      <c r="AV5" s="47"/>
+      <c r="AW5" s="47"/>
+      <c r="AX5" s="47"/>
+      <c r="AY5" s="47"/>
+      <c r="AZ5" s="48"/>
+      <c r="BA5" s="46">
         <f>BA6</f>
         <v>45957</v>
       </c>
-      <c r="BB5" s="51"/>
-      <c r="BC5" s="51"/>
-      <c r="BD5" s="51"/>
-      <c r="BE5" s="51"/>
-      <c r="BF5" s="51"/>
-      <c r="BG5" s="52"/>
-      <c r="BH5" s="50">
+      <c r="BB5" s="47"/>
+      <c r="BC5" s="47"/>
+      <c r="BD5" s="47"/>
+      <c r="BE5" s="47"/>
+      <c r="BF5" s="47"/>
+      <c r="BG5" s="48"/>
+      <c r="BH5" s="46">
         <f>BH6</f>
         <v>45964</v>
       </c>
-      <c r="BI5" s="51"/>
-      <c r="BJ5" s="51"/>
-      <c r="BK5" s="51"/>
-      <c r="BL5" s="51"/>
-      <c r="BM5" s="51"/>
-      <c r="BN5" s="52"/>
+      <c r="BI5" s="47"/>
+      <c r="BJ5" s="47"/>
+      <c r="BK5" s="47"/>
+      <c r="BL5" s="47"/>
+      <c r="BM5" s="47"/>
+      <c r="BN5" s="48"/>
     </row>
     <row r="6" spans="1:66" x14ac:dyDescent="0.2">
       <c r="B6" s="6"/>
@@ -3098,7 +3098,7 @@
         <v>6</v>
       </c>
       <c r="H16" s="11">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I16" s="12">
         <f t="shared" si="5"/>
@@ -3264,7 +3264,7 @@
         <v>7</v>
       </c>
       <c r="H18" s="11">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I18" s="12">
         <f t="shared" si="4"/>
@@ -3430,7 +3430,7 @@
         <v>5</v>
       </c>
       <c r="H20" s="11">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I20" s="12">
         <f t="shared" ref="I20" si="6">IF(OR(F20=0,E20=0)," - ",NETWORKDAYS(E20,F20))</f>
@@ -3762,7 +3762,7 @@
         <v>3</v>
       </c>
       <c r="H24" s="11">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="I24" s="12">
         <f t="shared" si="4"/>
@@ -4908,6 +4908,16 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0"/>
   <mergeCells count="20">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K1:AB1"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="R5:X5"/>
+    <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="Y4:AE4"/>
+    <mergeCell ref="Y5:AE5"/>
     <mergeCell ref="AF4:AL4"/>
     <mergeCell ref="AF5:AL5"/>
     <mergeCell ref="BH4:BN4"/>
@@ -4918,16 +4928,6 @@
     <mergeCell ref="AM4:AS4"/>
     <mergeCell ref="BA4:BG4"/>
     <mergeCell ref="BA5:BG5"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K1:AB1"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="R4:X4"/>
-    <mergeCell ref="K4:Q4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="R5:X5"/>
-    <mergeCell ref="K5:Q5"/>
-    <mergeCell ref="Y4:AE4"/>
-    <mergeCell ref="Y5:AE5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H8:H37">
@@ -4969,7 +4969,7 @@
   <pageSetup scale="63" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <ignoredErrors>
-    <ignoredError sqref="G12 G11 G17 G10 G9 G33:H36 H25 H24 H28:H31" unlockedFormula="1"/>
+    <ignoredError sqref="G12 G11 G17 G10 G9 G33:H36 H25 H28:H31" unlockedFormula="1"/>
   </ignoredErrors>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>

--- a/Plano de Projeto/Cronograma.xlsx
+++ b/Plano de Projeto/Cronograma.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guiba\Desktop\LDS\Plano de Projeto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8736636C-F279-4294-96B1-94208074A2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71CF8BA-BD01-4B8E-B7C7-587C9230BB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1048,24 +1048,6 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1076,9 +1058,27 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="31" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1252,7 +1252,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="22" fmlaLink="$H$4" horiz="1" max="100" min="1" page="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="22" fmlaLink="$H$4" horiz="1" max="100" min="1" page="0" val="6"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1683,26 +1683,26 @@
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="50" t="s">
+      <c r="K1" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
+      <c r="W1" s="44"/>
+      <c r="X1" s="44"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="44"/>
+      <c r="AA1" s="44"/>
+      <c r="AB1" s="44"/>
       <c r="AC1" s="42"/>
       <c r="AD1" s="42"/>
       <c r="AE1" s="42"/>
@@ -1742,191 +1742,191 @@
       <c r="B4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="52">
+      <c r="C4" s="49">
         <v>45915</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="49" t="s">
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="49"/>
+      <c r="G4" s="43"/>
       <c r="H4" s="30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="6"/>
-      <c r="K4" s="43" t="str">
+      <c r="K4" s="46" t="str">
         <f>"Semana "&amp;(K6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
-        <v>Semana 1</v>
-      </c>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="43" t="str">
+        <v>Semana 6</v>
+      </c>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="46" t="str">
         <f>"Semana "&amp;(R6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
-        <v>Semana 2</v>
-      </c>
-      <c r="S4" s="44"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44"/>
-      <c r="V4" s="44"/>
-      <c r="W4" s="44"/>
-      <c r="X4" s="45"/>
-      <c r="Y4" s="43" t="str">
+        <v>Semana 7</v>
+      </c>
+      <c r="S4" s="47"/>
+      <c r="T4" s="47"/>
+      <c r="U4" s="47"/>
+      <c r="V4" s="47"/>
+      <c r="W4" s="47"/>
+      <c r="X4" s="48"/>
+      <c r="Y4" s="46" t="str">
         <f>"Semana "&amp;(Y6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
-        <v>Semana 3</v>
-      </c>
-      <c r="Z4" s="44"/>
-      <c r="AA4" s="44"/>
-      <c r="AB4" s="44"/>
-      <c r="AC4" s="44"/>
-      <c r="AD4" s="44"/>
-      <c r="AE4" s="45"/>
-      <c r="AF4" s="43" t="str">
+        <v>Semana 8</v>
+      </c>
+      <c r="Z4" s="47"/>
+      <c r="AA4" s="47"/>
+      <c r="AB4" s="47"/>
+      <c r="AC4" s="47"/>
+      <c r="AD4" s="47"/>
+      <c r="AE4" s="48"/>
+      <c r="AF4" s="46" t="str">
         <f>"Semana "&amp;(AF6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
-        <v>Semana 4</v>
-      </c>
-      <c r="AG4" s="44"/>
-      <c r="AH4" s="44"/>
-      <c r="AI4" s="44"/>
-      <c r="AJ4" s="44"/>
-      <c r="AK4" s="44"/>
-      <c r="AL4" s="45"/>
-      <c r="AM4" s="43" t="str">
+        <v>Semana 9</v>
+      </c>
+      <c r="AG4" s="47"/>
+      <c r="AH4" s="47"/>
+      <c r="AI4" s="47"/>
+      <c r="AJ4" s="47"/>
+      <c r="AK4" s="47"/>
+      <c r="AL4" s="48"/>
+      <c r="AM4" s="46" t="str">
         <f>"Semana "&amp;(AM6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
-        <v>Semana 5</v>
-      </c>
-      <c r="AN4" s="44"/>
-      <c r="AO4" s="44"/>
-      <c r="AP4" s="44"/>
-      <c r="AQ4" s="44"/>
-      <c r="AR4" s="44"/>
-      <c r="AS4" s="45"/>
-      <c r="AT4" s="43" t="str">
+        <v>Semana 10</v>
+      </c>
+      <c r="AN4" s="47"/>
+      <c r="AO4" s="47"/>
+      <c r="AP4" s="47"/>
+      <c r="AQ4" s="47"/>
+      <c r="AR4" s="47"/>
+      <c r="AS4" s="48"/>
+      <c r="AT4" s="46" t="str">
         <f>"Semana "&amp;(AT6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
-        <v>Semana 6</v>
-      </c>
-      <c r="AU4" s="44"/>
-      <c r="AV4" s="44"/>
-      <c r="AW4" s="44"/>
-      <c r="AX4" s="44"/>
-      <c r="AY4" s="44"/>
-      <c r="AZ4" s="45"/>
-      <c r="BA4" s="43" t="str">
+        <v>Semana 11</v>
+      </c>
+      <c r="AU4" s="47"/>
+      <c r="AV4" s="47"/>
+      <c r="AW4" s="47"/>
+      <c r="AX4" s="47"/>
+      <c r="AY4" s="47"/>
+      <c r="AZ4" s="48"/>
+      <c r="BA4" s="46" t="str">
         <f>"Semana "&amp;(BA6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
-        <v>Semana 7</v>
-      </c>
-      <c r="BB4" s="44"/>
-      <c r="BC4" s="44"/>
-      <c r="BD4" s="44"/>
-      <c r="BE4" s="44"/>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="45"/>
-      <c r="BH4" s="43" t="str">
+        <v>Semana 12</v>
+      </c>
+      <c r="BB4" s="47"/>
+      <c r="BC4" s="47"/>
+      <c r="BD4" s="47"/>
+      <c r="BE4" s="47"/>
+      <c r="BF4" s="47"/>
+      <c r="BG4" s="48"/>
+      <c r="BH4" s="46" t="str">
         <f>"Semana "&amp;(BH6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
-        <v>Semana 8</v>
-      </c>
-      <c r="BI4" s="44"/>
-      <c r="BJ4" s="44"/>
-      <c r="BK4" s="44"/>
-      <c r="BL4" s="44"/>
-      <c r="BM4" s="44"/>
-      <c r="BN4" s="45"/>
+        <v>Semana 13</v>
+      </c>
+      <c r="BI4" s="47"/>
+      <c r="BJ4" s="47"/>
+      <c r="BK4" s="47"/>
+      <c r="BL4" s="47"/>
+      <c r="BM4" s="47"/>
+      <c r="BN4" s="48"/>
     </row>
     <row r="5" spans="1:66" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="19"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
       <c r="F5" s="18"/>
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="18"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="46">
+      <c r="K5" s="50">
         <f>K6</f>
-        <v>45915</v>
-      </c>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="46">
+        <v>45950</v>
+      </c>
+      <c r="L5" s="51"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="51"/>
+      <c r="O5" s="51"/>
+      <c r="P5" s="51"/>
+      <c r="Q5" s="52"/>
+      <c r="R5" s="50">
         <f>R6</f>
-        <v>45922</v>
-      </c>
-      <c r="S5" s="47"/>
-      <c r="T5" s="47"/>
-      <c r="U5" s="47"/>
-      <c r="V5" s="47"/>
-      <c r="W5" s="47"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="46">
+        <v>45957</v>
+      </c>
+      <c r="S5" s="51"/>
+      <c r="T5" s="51"/>
+      <c r="U5" s="51"/>
+      <c r="V5" s="51"/>
+      <c r="W5" s="51"/>
+      <c r="X5" s="52"/>
+      <c r="Y5" s="50">
         <f>Y6</f>
-        <v>45929</v>
-      </c>
-      <c r="Z5" s="47"/>
-      <c r="AA5" s="47"/>
-      <c r="AB5" s="47"/>
-      <c r="AC5" s="47"/>
-      <c r="AD5" s="47"/>
-      <c r="AE5" s="48"/>
-      <c r="AF5" s="46">
+        <v>45964</v>
+      </c>
+      <c r="Z5" s="51"/>
+      <c r="AA5" s="51"/>
+      <c r="AB5" s="51"/>
+      <c r="AC5" s="51"/>
+      <c r="AD5" s="51"/>
+      <c r="AE5" s="52"/>
+      <c r="AF5" s="50">
         <f>AF6</f>
-        <v>45936</v>
-      </c>
-      <c r="AG5" s="47"/>
-      <c r="AH5" s="47"/>
-      <c r="AI5" s="47"/>
-      <c r="AJ5" s="47"/>
-      <c r="AK5" s="47"/>
-      <c r="AL5" s="48"/>
-      <c r="AM5" s="46">
+        <v>45971</v>
+      </c>
+      <c r="AG5" s="51"/>
+      <c r="AH5" s="51"/>
+      <c r="AI5" s="51"/>
+      <c r="AJ5" s="51"/>
+      <c r="AK5" s="51"/>
+      <c r="AL5" s="52"/>
+      <c r="AM5" s="50">
         <f>AM6</f>
-        <v>45943</v>
-      </c>
-      <c r="AN5" s="47"/>
-      <c r="AO5" s="47"/>
-      <c r="AP5" s="47"/>
-      <c r="AQ5" s="47"/>
-      <c r="AR5" s="47"/>
-      <c r="AS5" s="48"/>
-      <c r="AT5" s="46">
+        <v>45978</v>
+      </c>
+      <c r="AN5" s="51"/>
+      <c r="AO5" s="51"/>
+      <c r="AP5" s="51"/>
+      <c r="AQ5" s="51"/>
+      <c r="AR5" s="51"/>
+      <c r="AS5" s="52"/>
+      <c r="AT5" s="50">
         <f>AT6</f>
-        <v>45950</v>
-      </c>
-      <c r="AU5" s="47"/>
-      <c r="AV5" s="47"/>
-      <c r="AW5" s="47"/>
-      <c r="AX5" s="47"/>
-      <c r="AY5" s="47"/>
-      <c r="AZ5" s="48"/>
-      <c r="BA5" s="46">
+        <v>45985</v>
+      </c>
+      <c r="AU5" s="51"/>
+      <c r="AV5" s="51"/>
+      <c r="AW5" s="51"/>
+      <c r="AX5" s="51"/>
+      <c r="AY5" s="51"/>
+      <c r="AZ5" s="52"/>
+      <c r="BA5" s="50">
         <f>BA6</f>
-        <v>45957</v>
-      </c>
-      <c r="BB5" s="47"/>
-      <c r="BC5" s="47"/>
-      <c r="BD5" s="47"/>
-      <c r="BE5" s="47"/>
-      <c r="BF5" s="47"/>
-      <c r="BG5" s="48"/>
-      <c r="BH5" s="46">
+        <v>45992</v>
+      </c>
+      <c r="BB5" s="51"/>
+      <c r="BC5" s="51"/>
+      <c r="BD5" s="51"/>
+      <c r="BE5" s="51"/>
+      <c r="BF5" s="51"/>
+      <c r="BG5" s="52"/>
+      <c r="BH5" s="50">
         <f>BH6</f>
-        <v>45964</v>
-      </c>
-      <c r="BI5" s="47"/>
-      <c r="BJ5" s="47"/>
-      <c r="BK5" s="47"/>
-      <c r="BL5" s="47"/>
-      <c r="BM5" s="47"/>
-      <c r="BN5" s="48"/>
+        <v>45999</v>
+      </c>
+      <c r="BI5" s="51"/>
+      <c r="BJ5" s="51"/>
+      <c r="BK5" s="51"/>
+      <c r="BL5" s="51"/>
+      <c r="BM5" s="51"/>
+      <c r="BN5" s="52"/>
     </row>
     <row r="6" spans="1:66" x14ac:dyDescent="0.2">
       <c r="B6" s="6"/>
@@ -1940,227 +1940,227 @@
       <c r="J6" s="6"/>
       <c r="K6" s="14">
         <f>C4-WEEKDAY(C4,1)+2+7*(H4-1)</f>
-        <v>45915</v>
+        <v>45950</v>
       </c>
       <c r="L6" s="13">
         <f t="shared" ref="L6:AQ6" si="0">K6+1</f>
-        <v>45916</v>
+        <v>45951</v>
       </c>
       <c r="M6" s="13">
         <f t="shared" si="0"/>
-        <v>45917</v>
+        <v>45952</v>
       </c>
       <c r="N6" s="13">
         <f t="shared" si="0"/>
-        <v>45918</v>
+        <v>45953</v>
       </c>
       <c r="O6" s="13">
         <f t="shared" si="0"/>
-        <v>45919</v>
+        <v>45954</v>
       </c>
       <c r="P6" s="13">
         <f t="shared" si="0"/>
-        <v>45920</v>
+        <v>45955</v>
       </c>
       <c r="Q6" s="15">
         <f t="shared" si="0"/>
-        <v>45921</v>
+        <v>45956</v>
       </c>
       <c r="R6" s="14">
         <f t="shared" si="0"/>
-        <v>45922</v>
+        <v>45957</v>
       </c>
       <c r="S6" s="13">
         <f t="shared" si="0"/>
-        <v>45923</v>
+        <v>45958</v>
       </c>
       <c r="T6" s="13">
         <f t="shared" si="0"/>
-        <v>45924</v>
+        <v>45959</v>
       </c>
       <c r="U6" s="13">
         <f t="shared" si="0"/>
-        <v>45925</v>
+        <v>45960</v>
       </c>
       <c r="V6" s="13">
         <f t="shared" si="0"/>
-        <v>45926</v>
+        <v>45961</v>
       </c>
       <c r="W6" s="13">
         <f t="shared" si="0"/>
-        <v>45927</v>
+        <v>45962</v>
       </c>
       <c r="X6" s="15">
         <f t="shared" si="0"/>
-        <v>45928</v>
+        <v>45963</v>
       </c>
       <c r="Y6" s="14">
         <f t="shared" si="0"/>
-        <v>45929</v>
+        <v>45964</v>
       </c>
       <c r="Z6" s="13">
         <f t="shared" si="0"/>
-        <v>45930</v>
+        <v>45965</v>
       </c>
       <c r="AA6" s="13">
         <f t="shared" si="0"/>
-        <v>45931</v>
+        <v>45966</v>
       </c>
       <c r="AB6" s="13">
         <f t="shared" si="0"/>
-        <v>45932</v>
+        <v>45967</v>
       </c>
       <c r="AC6" s="13">
         <f t="shared" si="0"/>
-        <v>45933</v>
+        <v>45968</v>
       </c>
       <c r="AD6" s="13">
         <f t="shared" si="0"/>
-        <v>45934</v>
+        <v>45969</v>
       </c>
       <c r="AE6" s="15">
         <f t="shared" si="0"/>
-        <v>45935</v>
+        <v>45970</v>
       </c>
       <c r="AF6" s="14">
         <f t="shared" si="0"/>
-        <v>45936</v>
+        <v>45971</v>
       </c>
       <c r="AG6" s="13">
         <f t="shared" si="0"/>
-        <v>45937</v>
+        <v>45972</v>
       </c>
       <c r="AH6" s="13">
         <f t="shared" si="0"/>
-        <v>45938</v>
+        <v>45973</v>
       </c>
       <c r="AI6" s="13">
         <f t="shared" si="0"/>
-        <v>45939</v>
+        <v>45974</v>
       </c>
       <c r="AJ6" s="13">
         <f t="shared" si="0"/>
-        <v>45940</v>
+        <v>45975</v>
       </c>
       <c r="AK6" s="13">
         <f t="shared" si="0"/>
-        <v>45941</v>
+        <v>45976</v>
       </c>
       <c r="AL6" s="15">
         <f t="shared" si="0"/>
-        <v>45942</v>
+        <v>45977</v>
       </c>
       <c r="AM6" s="14">
         <f t="shared" si="0"/>
-        <v>45943</v>
+        <v>45978</v>
       </c>
       <c r="AN6" s="13">
         <f t="shared" si="0"/>
-        <v>45944</v>
+        <v>45979</v>
       </c>
       <c r="AO6" s="13">
         <f t="shared" si="0"/>
-        <v>45945</v>
+        <v>45980</v>
       </c>
       <c r="AP6" s="13">
         <f t="shared" si="0"/>
-        <v>45946</v>
+        <v>45981</v>
       </c>
       <c r="AQ6" s="13">
         <f t="shared" si="0"/>
-        <v>45947</v>
+        <v>45982</v>
       </c>
       <c r="AR6" s="13">
         <f t="shared" ref="AR6:BN6" si="1">AQ6+1</f>
-        <v>45948</v>
+        <v>45983</v>
       </c>
       <c r="AS6" s="15">
         <f t="shared" si="1"/>
-        <v>45949</v>
+        <v>45984</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="1"/>
-        <v>45950</v>
+        <v>45985</v>
       </c>
       <c r="AU6" s="13">
         <f t="shared" si="1"/>
-        <v>45951</v>
+        <v>45986</v>
       </c>
       <c r="AV6" s="13">
         <f t="shared" si="1"/>
-        <v>45952</v>
+        <v>45987</v>
       </c>
       <c r="AW6" s="13">
         <f t="shared" si="1"/>
-        <v>45953</v>
+        <v>45988</v>
       </c>
       <c r="AX6" s="13">
         <f t="shared" si="1"/>
-        <v>45954</v>
+        <v>45989</v>
       </c>
       <c r="AY6" s="13">
         <f t="shared" si="1"/>
-        <v>45955</v>
+        <v>45990</v>
       </c>
       <c r="AZ6" s="15">
         <f t="shared" si="1"/>
-        <v>45956</v>
+        <v>45991</v>
       </c>
       <c r="BA6" s="14">
         <f t="shared" si="1"/>
-        <v>45957</v>
+        <v>45992</v>
       </c>
       <c r="BB6" s="13">
         <f t="shared" si="1"/>
-        <v>45958</v>
+        <v>45993</v>
       </c>
       <c r="BC6" s="13">
         <f t="shared" si="1"/>
-        <v>45959</v>
+        <v>45994</v>
       </c>
       <c r="BD6" s="13">
         <f t="shared" si="1"/>
-        <v>45960</v>
+        <v>45995</v>
       </c>
       <c r="BE6" s="13">
         <f t="shared" si="1"/>
-        <v>45961</v>
+        <v>45996</v>
       </c>
       <c r="BF6" s="13">
         <f t="shared" si="1"/>
-        <v>45962</v>
+        <v>45997</v>
       </c>
       <c r="BG6" s="15">
         <f t="shared" si="1"/>
-        <v>45963</v>
+        <v>45998</v>
       </c>
       <c r="BH6" s="14">
         <f t="shared" si="1"/>
-        <v>45964</v>
+        <v>45999</v>
       </c>
       <c r="BI6" s="13">
         <f t="shared" si="1"/>
-        <v>45965</v>
+        <v>46000</v>
       </c>
       <c r="BJ6" s="13">
         <f t="shared" si="1"/>
-        <v>45966</v>
+        <v>46001</v>
       </c>
       <c r="BK6" s="13">
         <f t="shared" si="1"/>
-        <v>45967</v>
+        <v>46002</v>
       </c>
       <c r="BL6" s="13">
         <f t="shared" si="1"/>
-        <v>45968</v>
+        <v>46003</v>
       </c>
       <c r="BM6" s="13">
         <f t="shared" si="1"/>
-        <v>45969</v>
+        <v>46004</v>
       </c>
       <c r="BN6" s="15">
         <f t="shared" si="1"/>
-        <v>45970</v>
+        <v>46005</v>
       </c>
     </row>
     <row r="7" spans="1:66" s="2" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -3098,7 +3098,7 @@
         <v>6</v>
       </c>
       <c r="H16" s="11">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I16" s="12">
         <f t="shared" si="5"/>
@@ -3181,7 +3181,7 @@
         <v>7</v>
       </c>
       <c r="H17" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="12">
         <f t="shared" si="4"/>
@@ -3264,7 +3264,7 @@
         <v>7</v>
       </c>
       <c r="H18" s="11">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I18" s="12">
         <f t="shared" si="4"/>
@@ -3347,7 +3347,7 @@
         <v>4</v>
       </c>
       <c r="H19" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="12">
         <f t="shared" si="4"/>
@@ -3430,7 +3430,7 @@
         <v>5</v>
       </c>
       <c r="H20" s="11">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I20" s="12">
         <f t="shared" ref="I20" si="6">IF(OR(F20=0,E20=0)," - ",NETWORKDAYS(E20,F20))</f>
@@ -3513,7 +3513,7 @@
         <v>3</v>
       </c>
       <c r="H21" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="12">
         <f t="shared" si="4"/>
@@ -3596,7 +3596,7 @@
         <v>4</v>
       </c>
       <c r="H22" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="12">
         <f t="shared" ref="I22:I23" si="7">IF(OR(F22=0,E22=0)," - ",NETWORKDAYS(E22,F22))</f>
@@ -3679,7 +3679,7 @@
         <v>5</v>
       </c>
       <c r="H23" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="12">
         <f t="shared" si="7"/>
@@ -3762,7 +3762,7 @@
         <v>3</v>
       </c>
       <c r="H24" s="11">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I24" s="12">
         <f t="shared" si="4"/>
@@ -3845,7 +3845,7 @@
         <v>6</v>
       </c>
       <c r="H25" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="12">
         <f t="shared" si="4"/>
@@ -3928,7 +3928,7 @@
         <v>5</v>
       </c>
       <c r="H26" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="12">
         <f>IF(OR(F26=0,E26=0)," - ",NETWORKDAYS(E26,F26))</f>
@@ -4908,6 +4908,16 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0"/>
   <mergeCells count="20">
+    <mergeCell ref="AF4:AL4"/>
+    <mergeCell ref="AF5:AL5"/>
+    <mergeCell ref="BH4:BN4"/>
+    <mergeCell ref="BH5:BN5"/>
+    <mergeCell ref="AM5:AS5"/>
+    <mergeCell ref="AT4:AZ4"/>
+    <mergeCell ref="AT5:AZ5"/>
+    <mergeCell ref="AM4:AS4"/>
+    <mergeCell ref="BA4:BG4"/>
+    <mergeCell ref="BA5:BG5"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="K1:AB1"/>
     <mergeCell ref="C5:E5"/>
@@ -4918,16 +4928,6 @@
     <mergeCell ref="K5:Q5"/>
     <mergeCell ref="Y4:AE4"/>
     <mergeCell ref="Y5:AE5"/>
-    <mergeCell ref="AF4:AL4"/>
-    <mergeCell ref="AF5:AL5"/>
-    <mergeCell ref="BH4:BN4"/>
-    <mergeCell ref="BH5:BN5"/>
-    <mergeCell ref="AM5:AS5"/>
-    <mergeCell ref="AT4:AZ4"/>
-    <mergeCell ref="AT5:AZ5"/>
-    <mergeCell ref="AM4:AS4"/>
-    <mergeCell ref="BA4:BG4"/>
-    <mergeCell ref="BA5:BG5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H8:H37">
@@ -4969,7 +4969,7 @@
   <pageSetup scale="63" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <ignoredErrors>
-    <ignoredError sqref="G12 G11 G17 G10 G9 G33:H36 H25 H28:H31" unlockedFormula="1"/>
+    <ignoredError sqref="G12 G11 G17 G10 G9 G33:H36 H28:H31" unlockedFormula="1"/>
   </ignoredErrors>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
